--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.05529334970248551</v>
       </c>
       <c r="C2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>49096019</v>
+        <v>3530901</v>
       </c>
       <c r="L2" t="n">
-        <v>26952695</v>
+        <v>1674587</v>
       </c>
       <c r="M2" t="n">
-        <v>6524872</v>
+        <v>336855</v>
       </c>
       <c r="N2" t="n">
-        <v>333146</v>
+        <v>11781</v>
       </c>
       <c r="O2" t="n">
-        <v>3991813</v>
+        <v>216429</v>
       </c>
       <c r="P2" t="n">
-        <v>1658795</v>
+        <v>95181</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998975992202759</v>
+        <v>0.9997932314872742</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8341099619865417</v>
+        <v>0.719780445098877</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6876384615898132</v>
+        <v>0.5125172138214111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5939447283744812</v>
+        <v>0.3685785531997681</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4088493585586548</v>
+        <v>0.1745204031467438</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6527528762817383</v>
+        <v>0.4248787760734558</v>
       </c>
       <c r="W2" t="n">
-        <v>0.717576801776886</v>
+        <v>0.4941489696502686</v>
       </c>
       <c r="X2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>47982023</v>
+        <v>3493153</v>
       </c>
       <c r="AG2" t="n">
-        <v>25073837</v>
+        <v>1600240</v>
       </c>
       <c r="AH2" t="n">
-        <v>5967639</v>
+        <v>317977</v>
       </c>
       <c r="AI2" t="n">
-        <v>310462</v>
+        <v>11503</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3684743</v>
+        <v>204180</v>
       </c>
       <c r="AK2" t="n">
-        <v>1561091</v>
+        <v>89730</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8097841143608093</v>
+        <v>0.7074398994445801</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6521316170692444</v>
+        <v>0.4994371235370636</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5369819402694702</v>
+        <v>0.3433476388454437</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2927406430244446</v>
+        <v>0.1301568299531937</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6043883562088013</v>
+        <v>0.4018864035606384</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6731289029121399</v>
+        <v>0.4642896056175232</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01737264878728136</v>
       </c>
       <c r="C3" t="n">
-        <v>2459</v>
+        <v>491</v>
       </c>
       <c r="D3" t="n">
-        <v>49096019</v>
+        <v>3530901</v>
       </c>
       <c r="E3" t="n">
-        <v>8733968</v>
+        <v>1144479</v>
       </c>
       <c r="F3" t="n">
-        <v>524641</v>
+        <v>100043</v>
       </c>
       <c r="G3" t="n">
-        <v>60586</v>
+        <v>8902</v>
       </c>
       <c r="H3" t="n">
-        <v>54378</v>
+        <v>15182</v>
       </c>
       <c r="I3" t="n">
-        <v>8929</v>
+        <v>2903</v>
       </c>
       <c r="J3" t="n">
-        <v>118283899</v>
+        <v>9856343</v>
       </c>
       <c r="K3" t="n">
-        <v>124599472</v>
+        <v>9892875</v>
       </c>
       <c r="L3" t="n">
-        <v>141515195</v>
+        <v>11161433</v>
       </c>
       <c r="M3" t="n">
-        <v>177172558</v>
+        <v>14550769</v>
       </c>
       <c r="N3" t="n">
-        <v>191295371</v>
+        <v>15925105</v>
       </c>
       <c r="O3" t="n">
-        <v>184598771</v>
+        <v>15265066</v>
       </c>
       <c r="P3" t="n">
-        <v>189869338</v>
+        <v>15778915</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8395211696624756</v>
+        <v>0.7351600527763367</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6895692944526672</v>
+        <v>0.5049751400947571</v>
       </c>
       <c r="T3" t="n">
-        <v>0.581982433795929</v>
+        <v>0.357384592294693</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3120113015174866</v>
+        <v>0.1315269470214844</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6519916653633118</v>
+        <v>0.4224051535129547</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7141990065574646</v>
+        <v>0.4904972910881042</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47982023</v>
+        <v>3493153</v>
       </c>
       <c r="Z3" t="n">
-        <v>9522879</v>
+        <v>1148330</v>
       </c>
       <c r="AA3" t="n">
-        <v>700350</v>
+        <v>117926</v>
       </c>
       <c r="AB3" t="n">
-        <v>191118</v>
+        <v>21139</v>
       </c>
       <c r="AC3" t="n">
-        <v>71585</v>
+        <v>18489</v>
       </c>
       <c r="AD3" t="n">
-        <v>13025</v>
+        <v>3864</v>
       </c>
       <c r="AE3" t="n">
-        <v>118291536</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>123092987</v>
+        <v>9822914</v>
       </c>
       <c r="AG3" t="n">
-        <v>140383319</v>
+        <v>11150376</v>
       </c>
       <c r="AH3" t="n">
-        <v>176487684</v>
+        <v>14519713</v>
       </c>
       <c r="AI3" t="n">
-        <v>191026989</v>
+        <v>15903954</v>
       </c>
       <c r="AJ3" t="n">
-        <v>184310404</v>
+        <v>15254153</v>
       </c>
       <c r="AK3" t="n">
-        <v>189764140</v>
+        <v>15772817</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8204723000526428</v>
+        <v>0.7273006439208984</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6414998173713684</v>
+        <v>0.4825556576251984</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5322803258895874</v>
+        <v>0.3373560905456543</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.2907663583755493</v>
+        <v>0.1284232586622238</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6018372178077698</v>
+        <v>0.3984987437725067</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6721322536468506</v>
+        <v>0.4624066054821014</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.1069592155238431</v>
       </c>
       <c r="C4" t="n">
-        <v>949</v>
+        <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>8995029</v>
+        <v>1223084</v>
       </c>
       <c r="E4" t="n">
-        <v>26952695</v>
+        <v>1674587</v>
       </c>
       <c r="F4" t="n">
-        <v>2539028</v>
+        <v>309252</v>
       </c>
       <c r="G4" t="n">
-        <v>108718</v>
+        <v>15903</v>
       </c>
       <c r="H4" t="n">
-        <v>424203</v>
+        <v>78488</v>
       </c>
       <c r="I4" t="n">
-        <v>65652</v>
+        <v>14668</v>
       </c>
       <c r="J4" t="n">
-        <v>7637</v>
+        <v>1285</v>
       </c>
       <c r="K4" t="n">
-        <v>9764348</v>
+        <v>1374624</v>
       </c>
       <c r="L4" t="n">
-        <v>12243331</v>
+        <v>1592790</v>
       </c>
       <c r="M4" t="n">
-        <v>4460783</v>
+        <v>577075</v>
       </c>
       <c r="N4" t="n">
-        <v>481692</v>
+        <v>55724</v>
       </c>
       <c r="O4" t="n">
-        <v>2123538</v>
+        <v>292961</v>
       </c>
       <c r="P4" t="n">
-        <v>652867</v>
+        <v>97435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999487996101379</v>
+        <v>0.9998965859413147</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8368067741394043</v>
+        <v>0.7273889183998108</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6886025667190552</v>
+        <v>0.5087182521820068</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5879027247428894</v>
+        <v>0.362895280122757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.353925883769989</v>
+        <v>0.1500038206577301</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6523720622062683</v>
+        <v>0.4236383438110352</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7158839702606201</v>
+        <v>0.492316335439682</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>10316149</v>
+        <v>1270840</v>
       </c>
       <c r="Z4" t="n">
-        <v>25073837</v>
+        <v>1600240</v>
       </c>
       <c r="AA4" t="n">
-        <v>2907345</v>
+        <v>320069</v>
       </c>
       <c r="AB4" t="n">
-        <v>198806</v>
+        <v>23306</v>
       </c>
       <c r="AC4" t="n">
-        <v>507223</v>
+        <v>85088</v>
       </c>
       <c r="AD4" t="n">
-        <v>82914</v>
+        <v>16634</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>11270833</v>
+        <v>1444585</v>
       </c>
       <c r="AG4" t="n">
-        <v>13375207</v>
+        <v>1603847</v>
       </c>
       <c r="AH4" t="n">
-        <v>5145657</v>
+        <v>608131</v>
       </c>
       <c r="AI4" t="n">
-        <v>750074</v>
+        <v>76875</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2411905</v>
+        <v>303874</v>
       </c>
       <c r="AK4" t="n">
-        <v>758065</v>
+        <v>103533</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8150931596755981</v>
+        <v>0.7172327637672424</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.646772027015686</v>
+        <v>0.4908512830734253</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5346208214759827</v>
+        <v>0.3403254747390747</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2917501628398895</v>
+        <v>0.1292842328548431</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6031100153923035</v>
+        <v>0.4001854360103607</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.672630250453949</v>
+        <v>0.4633462131023407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1450</v>
+        <v>241</v>
       </c>
       <c r="D5" t="n">
-        <v>550350</v>
+        <v>111738</v>
       </c>
       <c r="E5" t="n">
-        <v>2780209</v>
+        <v>322934</v>
       </c>
       <c r="F5" t="n">
-        <v>6524872</v>
+        <v>336855</v>
       </c>
       <c r="G5" t="n">
-        <v>170901</v>
+        <v>16922</v>
       </c>
       <c r="H5" t="n">
-        <v>1029876</v>
+        <v>126677</v>
       </c>
       <c r="I5" t="n">
-        <v>153801</v>
+        <v>27189</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9384961</v>
+        <v>1272000</v>
       </c>
       <c r="L5" t="n">
-        <v>12133579</v>
+        <v>1641590</v>
       </c>
       <c r="M5" t="n">
-        <v>4686587</v>
+        <v>605701</v>
       </c>
       <c r="N5" t="n">
-        <v>734591</v>
+        <v>77790</v>
       </c>
       <c r="O5" t="n">
-        <v>2130678</v>
+        <v>295944</v>
       </c>
       <c r="P5" t="n">
-        <v>663800</v>
+        <v>98869</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999604225158691</v>
+        <v>0.9999200105667114</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9007009267807007</v>
+        <v>0.8353106379508972</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8735930919647217</v>
+        <v>0.7987368106842041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9525661468505859</v>
+        <v>0.926400363445282</v>
       </c>
       <c r="U5" t="n">
-        <v>0.993692934513092</v>
+        <v>0.9916919469833374</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9779396653175354</v>
+        <v>0.9633546471595764</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931724071502686</v>
+        <v>0.987784743309021</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>685286</v>
+        <v>127400</v>
       </c>
       <c r="Z5" t="n">
-        <v>3017666</v>
+        <v>321330</v>
       </c>
       <c r="AA5" t="n">
-        <v>5967639</v>
+        <v>317977</v>
       </c>
       <c r="AB5" t="n">
-        <v>201987</v>
+        <v>18196</v>
       </c>
       <c r="AC5" t="n">
-        <v>1155657</v>
+        <v>128388</v>
       </c>
       <c r="AD5" t="n">
-        <v>183224</v>
+        <v>29265</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>10498957</v>
+        <v>1309748</v>
       </c>
       <c r="AG5" t="n">
-        <v>14012437</v>
+        <v>1715937</v>
       </c>
       <c r="AH5" t="n">
-        <v>5243820</v>
+        <v>624579</v>
       </c>
       <c r="AI5" t="n">
-        <v>757275</v>
+        <v>78068</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2437748</v>
+        <v>308193</v>
       </c>
       <c r="AK5" t="n">
-        <v>761504</v>
+        <v>104320</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8871123790740967</v>
+        <v>0.8286083340644836</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8579809069633484</v>
+        <v>0.7934224605560303</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9461252093315125</v>
+        <v>0.9232931137084961</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9921836256980896</v>
+        <v>0.9903584718704224</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9748520255088806</v>
+        <v>0.9619134068489075</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9921202659606934</v>
+        <v>0.9870660901069641</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1881</v>
+        <v>237</v>
       </c>
       <c r="D6" t="n">
-        <v>152392</v>
+        <v>19189</v>
       </c>
       <c r="E6" t="n">
-        <v>210399</v>
+        <v>24714</v>
       </c>
       <c r="F6" t="n">
-        <v>216435</v>
+        <v>17376</v>
       </c>
       <c r="G6" t="n">
-        <v>333146</v>
+        <v>11781</v>
       </c>
       <c r="H6" t="n">
-        <v>129385</v>
+        <v>12986</v>
       </c>
       <c r="I6" t="n">
-        <v>24099</v>
+        <v>3288</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>175542</v>
+        <v>20393</v>
       </c>
       <c r="Z6" t="n">
-        <v>209618</v>
+        <v>24197</v>
       </c>
       <c r="AA6" t="n">
-        <v>205739</v>
+        <v>17122</v>
       </c>
       <c r="AB6" t="n">
-        <v>310462</v>
+        <v>11503</v>
       </c>
       <c r="AC6" t="n">
-        <v>139172</v>
+        <v>12946</v>
       </c>
       <c r="AD6" t="n">
-        <v>27204</v>
+        <v>3410</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>591</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>61998</v>
+        <v>18620</v>
       </c>
       <c r="E7" t="n">
-        <v>467970</v>
+        <v>88664</v>
       </c>
       <c r="F7" t="n">
-        <v>1077528</v>
+        <v>128381</v>
       </c>
       <c r="G7" t="n">
-        <v>122205</v>
+        <v>10805</v>
       </c>
       <c r="H7" t="n">
-        <v>3991813</v>
+        <v>216429</v>
       </c>
       <c r="I7" t="n">
-        <v>400386</v>
+        <v>49387</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>86211</v>
+        <v>22972</v>
       </c>
       <c r="Z7" t="n">
-        <v>561132</v>
+        <v>96320</v>
       </c>
       <c r="AA7" t="n">
-        <v>1203889</v>
+        <v>127732</v>
       </c>
       <c r="AB7" t="n">
-        <v>134818</v>
+        <v>10809</v>
       </c>
       <c r="AC7" t="n">
-        <v>3684743</v>
+        <v>204180</v>
       </c>
       <c r="AD7" t="n">
-        <v>451698</v>
+        <v>50360</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>4579</v>
+        <v>1993</v>
       </c>
       <c r="E8" t="n">
-        <v>50785</v>
+        <v>11999</v>
       </c>
       <c r="F8" t="n">
-        <v>103151</v>
+        <v>22023</v>
       </c>
       <c r="G8" t="n">
-        <v>19282</v>
+        <v>3192</v>
       </c>
       <c r="H8" t="n">
-        <v>485696</v>
+        <v>59628</v>
       </c>
       <c r="I8" t="n">
-        <v>1658795</v>
+        <v>95181</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7645</v>
+        <v>2980</v>
       </c>
       <c r="Z8" t="n">
-        <v>63912</v>
+        <v>13670</v>
       </c>
       <c r="AA8" t="n">
-        <v>128334</v>
+        <v>25282</v>
       </c>
       <c r="AB8" t="n">
-        <v>23345</v>
+        <v>3425</v>
       </c>
       <c r="AC8" t="n">
-        <v>538268</v>
+        <v>58963</v>
       </c>
       <c r="AD8" t="n">
-        <v>1561091</v>
+        <v>89730</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
